--- a/Configs/source/Datas/mask.xlsx
+++ b/Configs/source/Datas/mask.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -65,19 +65,16 @@
     <t>本我</t>
   </si>
   <si>
-    <t>阎王</t>
-  </si>
-  <si>
-    <t>十殿阎罗</t>
-  </si>
-  <si>
-    <t>黑白无常</t>
-  </si>
-  <si>
-    <t>孟婆</t>
-  </si>
-  <si>
-    <t>二郎神</t>
+    <t>阎王面具</t>
+  </si>
+  <si>
+    <t>无常面具</t>
+  </si>
+  <si>
+    <t>孟婆面具</t>
+  </si>
+  <si>
+    <t>二郎神面具</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1143,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:4">
@@ -1167,14 +1164,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
+    <row r="10" spans="3:3">
       <c r="C10" s="4"/>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="2:3">
       <c r="B11" s="4"/>

--- a/Configs/source/Datas/mask.xlsx
+++ b/Configs/source/Datas/mask.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="MaskTable" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>无常面具</t>
+  </si>
+  <si>
+    <t>阎罗面具</t>
   </si>
   <si>
     <t>孟婆面具</t>
@@ -730,7 +733,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -744,6 +747,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1068,14 +1074,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
-    <col min="3" max="3" width="20.9732142857143" customWidth="1"/>
-    <col min="4" max="4" width="15.1696428571429" customWidth="1"/>
-    <col min="5" max="5" width="11.6071428571429" customWidth="1"/>
-    <col min="6" max="6" width="10.4196428571429" customWidth="1"/>
+    <col min="2" max="2" width="32.8916666666667" customWidth="1"/>
+    <col min="3" max="3" width="20.975" customWidth="1"/>
+    <col min="4" max="4" width="15.1666666666667" customWidth="1"/>
+    <col min="5" max="5" width="11.6083333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.4166666666667" customWidth="1"/>
     <col min="7" max="7" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1107,12 +1113,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" spans="1:1">
+    <row r="3" s="3" customFormat="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:3">
+    <row r="4" s="1" customFormat="1" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1120,7 +1126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="1:4">
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -1129,7 +1135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="1:4">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -1138,24 +1144,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="1:4">
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="5"/>
       <c r="D8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="1:4">
       <c r="B9" t="s">
         <v>15</v>
       </c>
@@ -1164,49 +1170,58 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:3">
+    <row r="10" spans="1:4">
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
       <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="B11" s="4"/>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="2:3">
+    <row r="12" spans="1:4">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="5"/>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="5"/>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="5"/>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" s="5"/>
+    <row r="13" spans="1:4">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="6"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" s="6"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" s="6"/>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="5"/>
+      <c r="B17" s="6"/>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="5"/>
+      <c r="B18" s="6"/>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="5"/>
+      <c r="B19" s="6"/>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="5"/>
+      <c r="B20" s="6"/>
     </row>
     <row r="21" spans="2:2">
-      <c r="B21" s="5"/>
+      <c r="B21" s="6"/>
     </row>
     <row r="22" spans="2:2">
-      <c r="B22" s="5"/>
+      <c r="B22" s="6"/>
     </row>
     <row r="23" spans="2:2">
-      <c r="B23" s="5"/>
+      <c r="B23" s="6"/>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/source/Datas/mask.xlsx
+++ b/Configs/source/Datas/mask.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="29100" windowHeight="12700"/>
   </bookViews>
   <sheets>
     <sheet name="MaskTable" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -65,19 +65,34 @@
     <t>本我</t>
   </si>
   <si>
+    <t>最真实的自己</t>
+  </si>
+  <si>
     <t>阎王面具</t>
   </si>
   <si>
+    <t>戴上时施加死期</t>
+  </si>
+  <si>
     <t>无常面具</t>
   </si>
   <si>
+    <t>黑白无常</t>
+  </si>
+  <si>
     <t>阎罗面具</t>
   </si>
   <si>
+    <t>XXX</t>
+  </si>
+  <si>
     <t>孟婆面具</t>
   </si>
   <si>
     <t>二郎神面具</t>
+  </si>
+  <si>
+    <t>拜托了 二郎神大人</t>
   </si>
 </sst>
 </file>
@@ -1075,13 +1090,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="32.8916666666667" customWidth="1"/>
-    <col min="3" max="3" width="20.975" customWidth="1"/>
-    <col min="4" max="4" width="15.1666666666667" customWidth="1"/>
-    <col min="5" max="5" width="11.6083333333333" customWidth="1"/>
-    <col min="6" max="6" width="10.4166666666667" customWidth="1"/>
+    <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
+    <col min="3" max="3" width="20.9732142857143" customWidth="1"/>
+    <col min="4" max="4" width="15.1696428571429" customWidth="1"/>
+    <col min="5" max="5" width="11.6071428571429" customWidth="1"/>
+    <col min="6" max="6" width="10.4196428571429" customWidth="1"/>
     <col min="7" max="7" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1113,12 +1128,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" spans="1:4">
+    <row r="3" s="3" customFormat="1" spans="1:1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:4">
+    <row r="4" s="1" customFormat="1" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1126,77 +1141,90 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="2:4">
       <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="2:4">
       <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="2:4">
       <c r="B7" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="2:4">
       <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="2:4">
       <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="2:4">
       <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="3:3">
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="2:3">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="2:3">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="2:2">
       <c r="B14" s="6"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="2:2">
       <c r="B15" s="6"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="2:2">
       <c r="B16" s="6"/>
     </row>
     <row r="17" spans="2:2">

--- a/Configs/source/Datas/mask.xlsx
+++ b/Configs/source/Datas/mask.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="MaskTable" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -71,28 +71,31 @@
     <t>阎王面具</t>
   </si>
   <si>
-    <t>戴上时施加死期</t>
+    <t>阎王将会宣判死期</t>
   </si>
   <si>
     <t>无常面具</t>
   </si>
   <si>
-    <t>黑白无常</t>
+    <t>一人勾魂，一人索命</t>
   </si>
   <si>
     <t>阎罗面具</t>
   </si>
   <si>
-    <t>XXX</t>
+    <t>十殿阎罗颁布律令！</t>
   </si>
   <si>
     <t>孟婆面具</t>
   </si>
   <si>
+    <t>喝了这碗汤，该上路了……</t>
+  </si>
+  <si>
     <t>二郎神面具</t>
   </si>
   <si>
-    <t>拜托了 二郎神大人</t>
+    <t>哮天犬？</t>
   </si>
 </sst>
 </file>
@@ -1090,13 +1093,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
-    <col min="3" max="3" width="20.9732142857143" customWidth="1"/>
-    <col min="4" max="4" width="15.1696428571429" customWidth="1"/>
-    <col min="5" max="5" width="11.6071428571429" customWidth="1"/>
-    <col min="6" max="6" width="10.4196428571429" customWidth="1"/>
+    <col min="2" max="2" width="32.8916666666667" customWidth="1"/>
+    <col min="3" max="3" width="20.975" customWidth="1"/>
+    <col min="4" max="4" width="15.1666666666667" customWidth="1"/>
+    <col min="5" max="5" width="11.6083333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.4166666666667" customWidth="1"/>
     <col min="7" max="7" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1128,12 +1131,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" spans="1:1">
+    <row r="3" s="3" customFormat="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:3">
+    <row r="4" s="1" customFormat="1" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1141,7 +1144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="1:4">
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -1152,7 +1155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="1:4">
       <c r="B6" t="s">
         <v>13</v>
       </c>
@@ -1163,7 +1166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="1:4">
       <c r="B7" t="s">
         <v>15</v>
       </c>
@@ -1174,7 +1177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="1:4">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -1185,46 +1188,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="1:4">
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="1:4">
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:3">
+    <row r="11" spans="1:4">
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="2:3">
+    <row r="12" spans="1:4">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="2:3">
+    <row r="13" spans="1:4">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="2:2">
+    <row r="14" spans="1:4">
       <c r="B14" s="6"/>
     </row>
-    <row r="15" spans="2:2">
+    <row r="15" spans="1:4">
       <c r="B15" s="6"/>
     </row>
-    <row r="16" spans="2:2">
+    <row r="16" spans="1:4">
       <c r="B16" s="6"/>
     </row>
     <row r="17" spans="2:2">
